--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="202">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -403,6 +403,237 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Consent
 </t>
+  </si>
+  <si>
+    <t>Consentement</t>
+  </si>
+  <si>
+    <t>Authorization.consent.nullFlavor</t>
+  </si>
+  <si>
+    <t>Authorization.consent.realmCode</t>
+  </si>
+  <si>
+    <t>Authorization.consent.typeId</t>
+  </si>
+  <si>
+    <t>Authorization.consent.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>Authorization.consent.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Authorization.consent.typeId.displayable</t>
+  </si>
+  <si>
+    <t>Authorization.consent.typeId.root</t>
+  </si>
+  <si>
+    <t>Authorization.consent.typeId.extension</t>
+  </si>
+  <si>
+    <t>Authorization.consent.templateId</t>
+  </si>
+  <si>
+    <t>Authorization.consent.classCode</t>
+  </si>
+  <si>
+    <t>CONS</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAActClass</t>
+  </si>
+  <si>
+    <t>Consent.classCode</t>
+  </si>
+  <si>
+    <t>Authorization.consent.moodCode</t>
+  </si>
+  <si>
+    <t>EVN</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAActMood</t>
+  </si>
+  <si>
+    <t>Consent.moodCode</t>
+  </si>
+  <si>
+    <t>Authorization.consent.id</t>
+  </si>
+  <si>
+    <t>Identifiant du consentement</t>
+  </si>
+  <si>
+    <t>Consent.id</t>
+  </si>
+  <si>
+    <t>Authorization.consent.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
+</t>
+  </si>
+  <si>
+    <t>Type de consentement</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
+  </si>
+  <si>
+    <t>Consent.code</t>
+  </si>
+  <si>
+    <t>Authorization.consent.statusCode</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActStatus</t>
+  </si>
+  <si>
+    <t>Consent.statusCode</t>
+  </si>
+  <si>
+    <t>Authorization.consent.statusCode.nullFlavor</t>
+  </si>
+  <si>
+    <t>Authorization.consent.statusCode.code</t>
+  </si>
+  <si>
+    <t>Valeur fixée à 'completed' car on enregistre que 
+les consentements obtenus</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>Consents referenced in the CDA Header have been finalized (Consent.statusCode must equal "completed") and should be on file.</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Authorization.consent.statusCode.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Authorization.consent.statusCode.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Authorization.consent.statusCode.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Authorization.consent.statusCode.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Authorization.consent.statusCode.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Authorization.consent.statusCode.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Authorization.consent.statusCode.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Authorization.consent.statusCode.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Authorization.consent.statusCode.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CD
+</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
   </si>
 </sst>
 </file>
@@ -704,11 +935,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.88671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.88671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.5703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="51.5703125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
@@ -1282,7 +1513,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1383,7 +1614,7 @@
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1486,7 +1717,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1894,7 +2125,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2005,7 +2236,9 @@
       <c r="K13" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L13" s="2"/>
+      <c r="L13" t="s" s="2">
+        <v>127</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2074,6 +2307,2545 @@
         <v>74</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y14" s="2"/>
+      <c r="Z14" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L15" s="2"/>
+      <c r="M15" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y17" s="2"/>
+      <c r="Z17" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y23" s="2"/>
+      <c r="Z23" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y24" s="2"/>
+      <c r="Z24" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y26" s="2"/>
+      <c r="Z26" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y27" s="2"/>
+      <c r="Z27" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y28" s="2"/>
+      <c r="Z28" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L30" s="2"/>
+      <c r="M30" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L31" s="2"/>
+      <c r="M31" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,8 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Authorization, permet de documenter qu'un consentement éclairé a été obtenu et d'indiquer quel type de 
-consentement a été fourni.</t>
+    <t>Authorization, permet de documenter qu'un consentement éclairé a été obtenu et d'indiquer quel type de consentement a été fourni.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -502,8 +501,7 @@
     <t>Authorization.consent.statusCode.code</t>
   </si>
   <si>
-    <t>Valeur fixée à 'completed' car on enregistre que 
-les consentements obtenus</t>
+    <t>Valeur fixée à 'completed' car on enregistre que les consentements obtenus</t>
   </si>
   <si>
     <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="203">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,6 +311,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>Authorization.typeId.nullFlavor</t>
@@ -1487,7 +1491,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1495,10 +1499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1596,17 +1600,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1624,11 +1628,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1679,7 +1683,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1699,17 +1703,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1727,11 +1731,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1782,7 +1786,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1802,17 +1806,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1830,11 +1834,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1843,7 +1847,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1885,7 +1889,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1905,17 +1909,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1933,11 +1937,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1988,7 +1992,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2008,10 +2012,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2038,7 +2042,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2089,7 +2093,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2109,10 +2113,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2146,7 +2150,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2168,7 +2172,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2186,7 +2190,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2206,10 +2210,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2232,10 +2236,10 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2287,7 +2291,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2307,10 +2311,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2408,10 +2412,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2509,10 +2513,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2602,7 +2606,7 @@
         <v>74</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>74</v>
@@ -2610,10 +2614,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2711,17 +2715,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>80</v>
@@ -2739,11 +2743,11 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2794,7 +2798,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2814,17 +2818,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -2842,11 +2846,11 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2897,7 +2901,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2917,17 +2921,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>75</v>
@@ -2945,11 +2949,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2958,7 +2962,7 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>74</v>
@@ -3000,7 +3004,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3020,17 +3024,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>75</v>
@@ -3048,11 +3052,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3103,7 +3107,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3123,10 +3127,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3153,7 +3157,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3204,7 +3208,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3224,10 +3228,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3261,7 +3265,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>74</v>
@@ -3283,7 +3287,7 @@
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>74</v>
@@ -3301,7 +3305,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3321,10 +3325,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3358,7 +3362,7 @@
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>74</v>
@@ -3380,7 +3384,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>74</v>
@@ -3398,7 +3402,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3418,10 +3422,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3447,7 +3451,7 @@
         <v>95</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -3499,7 +3503,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3519,10 +3523,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3530,7 +3534,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>75</v>
@@ -3545,10 +3549,10 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -3576,11 +3580,11 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -3598,7 +3602,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3618,10 +3622,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3677,7 +3681,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -3695,7 +3699,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -3715,10 +3719,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3816,10 +3820,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3847,13 +3851,13 @@
         <v>85</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -3861,7 +3865,7 @@
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>74</v>
@@ -3903,7 +3907,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -3923,17 +3927,17 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
@@ -3951,11 +3955,11 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4006,7 +4010,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4026,17 +4030,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4054,11 +4058,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4109,7 +4113,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4129,17 +4133,17 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4157,11 +4161,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4212,7 +4216,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4232,17 +4236,17 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4260,11 +4264,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4315,7 +4319,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4335,10 +4339,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4361,11 +4365,11 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4416,7 +4420,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4436,10 +4440,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4462,11 +4466,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4517,7 +4521,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4537,17 +4541,17 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
@@ -4565,11 +4569,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4620,7 +4624,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4640,17 +4644,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -4668,11 +4672,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4723,7 +4727,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4743,17 +4747,17 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -4771,11 +4775,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4826,7 +4830,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Authorization, permet de documenter qu'un consentement éclairé a été obtenu et d'indiquer quel type de consentement a été fourni.</t>
+    <t>L'élément de l'en-tête du CDA authorization permet de documenter qu'un consentement éclairé a été obtenu et d'indiquer quel type de consentement a été fourni.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
